--- a/output/reports/mobility_report_summary.xlsx
+++ b/output/reports/mobility_report_summary.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="By Year" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="By Faculty" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -511,4 +512,120 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>faculty</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>graduates</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>graduates_with_mobility</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>mobility_share</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Business &amp; Economics</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>210</v>
+      </c>
+      <c r="C2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.286</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Health Sciences</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>110</v>
+      </c>
+      <c r="C3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.273</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>STEM</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>210</v>
+      </c>
+      <c r="C4" t="n">
+        <v>60</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.286</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Society &amp; Culture</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>110</v>
+      </c>
+      <c r="C5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.273</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>UP FHS</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>110</v>
+      </c>
+      <c r="C6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.273</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/reports/mobility_report_summary.xlsx
+++ b/output/reports/mobility_report_summary.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,28 +600,12 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D5" t="n">
-        <v>0.273</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>UP FHS</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>110</v>
-      </c>
-      <c r="C6" t="n">
-        <v>30</v>
-      </c>
-      <c r="D6" t="n">
         <v>0.273</v>
       </c>
     </row>
